--- a/src/test/resources/testdata/AuthTestData.xlsx
+++ b/src/test/resources/testdata/AuthTestData.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30015"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E34F23C0-A70E-430E-8FA6-03E06159C98B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{27CD735B-A804-4ECF-9326-28655CE28120}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="0" windowHeight="0" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="0" windowHeight="0" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="loginValid" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="41">
   <si>
     <t>email</t>
   </si>
@@ -84,15 +84,12 @@
     <t>Invalid credentials</t>
   </si>
   <si>
-    <t>AYOUBAMZIL@EMAIL.COM</t>
-  </si>
-  <si>
-    <t>Email case sensitive</t>
-  </si>
-  <si>
     <t>password123</t>
   </si>
   <si>
+    <t>Wrong password</t>
+  </si>
+  <si>
     <t>Wrong password case</t>
   </si>
   <si>
@@ -108,15 +105,21 @@
     <t>confirmPassword</t>
   </si>
   <si>
+    <t>aamzil</t>
+  </si>
+  <si>
+    <t>aamzil@email.com</t>
+  </si>
+  <si>
+    <t>Valid register</t>
+  </si>
+  <si>
+    <t>Empty username</t>
+  </si>
+  <si>
     <t>ayoubamzil</t>
   </si>
   <si>
-    <t>Valid register</t>
-  </si>
-  <si>
-    <t>Empty username</t>
-  </si>
-  <si>
     <t>Empty confirm password</t>
   </si>
   <si>
@@ -145,6 +148,9 @@
   </si>
   <si>
     <t>ab</t>
+  </si>
+  <si>
+    <t>ab@email.com</t>
   </si>
   <si>
     <t>Username must be at least 3 characters</t>
@@ -193,17 +199,18 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF2F4F8F"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFE8F5E9"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="1"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -236,28 +243,25 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -572,30 +576,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="21.95" customHeight="1">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="6" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:4">
-      <c r="A2" s="7" t="s">
+      <c r="A2" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" s="2" t="s">
+      <c r="B2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="1" t="s">
         <v>7</v>
       </c>
     </row>
@@ -609,7 +613,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
@@ -619,126 +623,99 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="21.95" customHeight="1">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="6" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:4">
-      <c r="A2" s="3"/>
-      <c r="B2" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" s="3" t="s">
+      <c r="A2" s="2"/>
+      <c r="B2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:4">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="3"/>
-      <c r="C3" s="3" t="s">
+      <c r="B3" s="2"/>
+      <c r="C3" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="2" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:4">
-      <c r="A4" s="3"/>
-      <c r="B4" s="3"/>
-      <c r="C4" s="3" t="s">
+      <c r="A4" s="2"/>
+      <c r="B4" s="2"/>
+      <c r="C4" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="D4" s="2" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:4">
-      <c r="A5" s="3" t="s">
+      <c r="A5" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="D5" s="2" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="6" spans="1:4">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="D6" s="3" t="s">
+      <c r="C6" s="2" t="s">
         <v>17</v>
       </c>
+      <c r="D6" s="2" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="7" spans="1:4">
-      <c r="A7" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="D7" s="3" t="s">
+      <c r="A7" s="2" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="8" spans="1:4">
-      <c r="A8" s="3" t="s">
+      <c r="B7" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B8" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4">
-      <c r="A9" s="3"/>
-      <c r="B9" s="3"/>
-      <c r="C9" s="3"/>
-      <c r="D9" s="3"/>
-    </row>
-    <row r="10" spans="1:4">
-      <c r="A10" s="5"/>
-      <c r="B10" s="5"/>
-      <c r="C10" s="5"/>
-      <c r="D10" s="5"/>
+      <c r="D7" s="2" t="s">
+        <v>20</v>
+      </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="A3" r:id="rId1" xr:uid="{D7383432-6416-4876-8D03-43CE7C0C0ED5}"/>
-    <hyperlink ref="A6" r:id="rId2" xr:uid="{3D6DE6D0-0546-496D-90D1-80508D889B58}"/>
-    <hyperlink ref="A7" r:id="rId3" xr:uid="{F48F11FE-93A8-4BA6-87DA-1D09D1DAD377}"/>
+    <hyperlink ref="A6" r:id="rId2" xr:uid="{F48F11FE-93A8-4BA6-87DA-1D09D1DAD377}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -756,36 +733,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="21.95" customHeight="1">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2" s="2" t="s">
+      <c r="B2" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="B2" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="E2" s="2" t="s">
+      <c r="C2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>25</v>
       </c>
     </row>
@@ -810,212 +787,213 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="21.95" customHeight="1">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="6" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:6">
-      <c r="A2" s="3"/>
-      <c r="B2" s="3" t="s">
+      <c r="A2" s="2"/>
+      <c r="B2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E2" s="3" t="s">
+      <c r="C2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="F2" s="2" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="3" spans="1:6">
-      <c r="A3" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="B3" s="3"/>
-      <c r="C3" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E3" s="3" t="s">
+      <c r="A3" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B3" s="2"/>
+      <c r="C3" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="F3" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:6">
-      <c r="A4" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="B4" s="3" t="s">
+      <c r="A4" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="3"/>
-      <c r="D4" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E4" s="3" t="s">
+      <c r="C4" s="2"/>
+      <c r="D4" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="F4" s="2" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:6">
-      <c r="A5" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="B5" s="3" t="s">
+      <c r="A5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D5" s="3"/>
-      <c r="E5" s="3" t="s">
+      <c r="C5" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="F5" s="3" t="s">
+      <c r="F5" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="2"/>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="2" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="3"/>
-      <c r="B6" s="3"/>
-      <c r="C6" s="3"/>
-      <c r="D6" s="3"/>
-      <c r="E6" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C7" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="E7" s="3" t="s">
+      <c r="C7" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D7" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="F7" s="3" t="s">
+      <c r="E7" s="2" t="s">
         <v>30</v>
       </c>
+      <c r="F7" s="2" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="8" spans="1:6" ht="24">
-      <c r="A8" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="B8" s="3" t="s">
+      <c r="A8" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C8" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="E8" s="6" t="s">
+      <c r="C8" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="F8" s="3" t="s">
+      <c r="D8" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E8" s="4" t="s">
         <v>33</v>
       </c>
+      <c r="F8" s="2" t="s">
+        <v>34</v>
+      </c>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="B9" s="3" t="s">
+      <c r="A9" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E9" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="C9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>21</v>
+      <c r="F9" s="2" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="B10" s="4" t="s">
+      <c r="A10" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B10" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="F10" s="3" t="s">
+      <c r="C10" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E10" s="2" t="s">
         <v>35</v>
       </c>
+      <c r="F10" s="2" t="s">
+        <v>36</v>
+      </c>
     </row>
     <row r="11" spans="1:6" ht="24">
-      <c r="A11" s="3" t="s">
-        <v>36</v>
+      <c r="A11" s="2" t="s">
+        <v>37</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E11" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="F11" s="3" t="s">
         <v>38</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>40</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="B10" r:id="rId1" xr:uid="{C37BBF62-9590-48CD-A2C6-18670A30321B}"/>
+    <hyperlink ref="B11" r:id="rId2" xr:uid="{0844A868-575E-44B7-9E90-5F6F092BC098}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
